--- a/auditoria_pendientes.xlsx
+++ b/auditoria_pendientes.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes" sheetId="1" r:id="R6ba265d3c36a4488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitacora" sheetId="2" r:id="Rb61f3b9f6b744ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="3" r:id="R5c9dcb372c204c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogos" sheetId="4" r:id="R5b0097b51d5e40a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes" sheetId="1" r:id="Rd81fba86aef04379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bitacora" sheetId="2" r:id="R929bccd42a3f44e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="3" r:id="Rbfb3cdacd89b47f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogos" sheetId="4" r:id="R7690c1a7016e4453"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48,7 +48,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -56,74 +56,28 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PendientesTable" displayName="PendientesTable" ref="A1:L2" headerRowCount="1">
-  <x:tableColumns count="12">
-    <x:tableColumn id="1" name="ID"/>
-    <x:tableColumn id="2" name="Fecha Creación"/>
-    <x:tableColumn id="3" name="Hotel"/>
-    <x:tableColumn id="4" name="Departamento"/>
-    <x:tableColumn id="5" name="Tipo de Incidencia"/>
-    <x:tableColumn id="6" name="Impacto"/>
-    <x:tableColumn id="7" name="Prioridad"/>
-    <x:tableColumn id="8" name="Estatus"/>
-    <x:tableColumn id="9" name="Fecha Compromiso"/>
-    <x:tableColumn id="10" name="Descripción"/>
-    <x:tableColumn id="11" name="Fecha Cierre"/>
-    <x:tableColumn id="12" name="Última Actualización"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BitacoraTable" displayName="BitacoraTable" ref="A1:G2" headerRowCount="1">
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="ID Pendiente"/>
-    <x:tableColumn id="2" name="Fecha"/>
-    <x:tableColumn id="3" name="Usuario"/>
-    <x:tableColumn id="4" name="Acción"/>
-    <x:tableColumn id="5" name="Comentario"/>
-    <x:tableColumn id="6" name="Estado Anterior"/>
-    <x:tableColumn id="7" name="Estado Nuevo"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="UsuariosTable" displayName="UsuariosTable" ref="A1:E3" headerRowCount="1">
-  <x:tableColumns count="5">
-    <x:tableColumn id="1" name="Usuario"/>
-    <x:tableColumn id="2" name="Password"/>
-    <x:tableColumn id="3" name="Nombre"/>
-    <x:tableColumn id="4" name="Rol"/>
-    <x:tableColumn id="5" name="Estado"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CatalogosTable" displayName="CatalogosTable" ref="A1:B40" headerRowCount="1">
-  <x:tableColumns count="2">
-    <x:tableColumn id="1" name="Categoria"/>
-    <x:tableColumn id="2" name="Valor"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -275,97 +229,60 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="40" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="45" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Fecha Creación</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Hotel</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
-        <x:v>Departamento</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>Tipo de Incidencia</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
+      <x:c r="D1" s="5" t="str">
+        <x:v>Departamento</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="str">
+        <x:v>Tipo de Incidencia</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="str">
         <x:v>Impacto</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Prioridad</x:v>
       </x:c>
-      <x:c r="H1" s="4" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Estatus</x:v>
       </x:c>
-      <x:c r="I1" s="4" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Fecha Compromiso</x:v>
       </x:c>
-      <x:c r="J1" s="4" t="str">
+      <x:c r="J1" s="10" t="str">
         <x:v>Descripción</x:v>
       </x:c>
-      <x:c r="K1" s="4" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>Fecha Cierre</x:v>
       </x:c>
-      <x:c r="L1" s="4" t="str">
+      <x:c r="L1" s="5" t="str">
         <x:v>Última Actualización</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>INC-2026-001</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>2026-05-08</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>5918 - MCB</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>Recepción</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>Cobro no realizado</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>Financiero</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>Alta</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>Pendiente</x:v>
-      </x:c>
-      <x:c r="I2" t="str"/>
-      <x:c r="J2" t="str">
-        <x:v>Pendiente de validar cobro no realizado en recepción.</x:v>
-      </x:c>
-      <x:c r="K2" t="str"/>
-      <x:c r="L2" t="str">
-        <x:v>2026-05-08 16:03:29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4e79ab17d08436f"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -373,64 +290,40 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>ID Pendiente</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Fecha</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Usuario</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Acción</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>Comentario</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Estado Anterior</x:v>
       </x:c>
-      <x:c r="G1" s="4" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Estado Nuevo</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>INC-2026-001</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>2026-05-08 16:03:30</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>admin</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>Creación</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>Incidencia creada.</x:v>
-      </x:c>
-      <x:c r="F2" t="str"/>
-      <x:c r="G2" t="str">
-        <x:v>Pendiente</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R524d49d60501456b"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -438,27 +331,27 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>Usuario</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Password</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Nombre</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Rol</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Estado</x:v>
       </x:c>
     </x:row>
@@ -498,9 +391,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd16f4e6fde57488e"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -508,15 +398,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>Categoria</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>Valor</x:v>
       </x:c>
     </x:row>
@@ -834,8 +724,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc739c3fd8e5f4944"/>
-  </x:tableParts>
 </x:worksheet>
 </file>